--- a/artfynd/A 31921-2026 artfynd.xlsx
+++ b/artfynd/A 31921-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135794538</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
